--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>1148.4</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PUEBLA GONZALEZ MARIO DANIEL</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VARIEDADES-PAS SAS</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2359,144 +2359,84 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>1 de 31</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="R33" s="4" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1148.4</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>4000</v>
@@ -3013,7 +2953,7 @@
         <v>54.72</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>35.81</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1500</v>
@@ -3300,7 +3240,7 @@
         <v>11295.33</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-71.11</v>
+        <v>1113.1</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3324,7 +3264,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3423,13 +3363,13 @@
         <v>3973</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>35.81</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3973</v>
+        <v>3937.19</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>0.009013340045305815</v>
       </c>
     </row>
     <row r="5">
@@ -3495,13 +3435,13 @@
         <v>655</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>1148.4</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>655</v>
+        <v>-493.4000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.753282442748092</v>
       </c>
     </row>
     <row r="8">
@@ -3706,13 +3646,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>256.66</v>
+        <v>1440.87</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>50307.783</v>
+        <v>49123.573</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.005075898888078328</v>
+        <v>0.02849571585313419</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>7495.2</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0</v>
+        <v>6982.18</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
@@ -2366,52 +2366,52 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>1 de 30</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>1 de 30</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>14477.38</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>10000</v>
@@ -3240,7 +3240,7 @@
         <v>11295.33</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1113.1</v>
+        <v>15590.48</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3263,9 +3263,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3339,13 +3339,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>7495.2</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3800</v>
+        <v>-3695.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1.972421052631579</v>
       </c>
     </row>
     <row r="4">
@@ -3603,13 +3603,13 @@
         <v>39283</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-71.11</v>
+        <v>6911.07</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>39354.11</v>
+        <v>32371.93</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-0.001810197795484052</v>
+        <v>0.1759303006389532</v>
       </c>
     </row>
     <row r="15">
@@ -3646,13 +3646,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1440.87</v>
+        <v>15918.25</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>49123.573</v>
+        <v>34646.193</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.02849571585313419</v>
+        <v>0.3148111411016631</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-71.11</v>
+        <v>216.47</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>2146.66</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>3 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2629,7 +2629,7 @@
         <v>71.11</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-71.11</v>
+        <v>216.47</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>500</v>
@@ -2980,7 +2980,7 @@
         <v>4927.44</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>2146.66</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>11295.33</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>15590.48</v>
+        <v>18024.72</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3603,13 +3603,13 @@
         <v>39283</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6911.07</v>
+        <v>9345.309999999999</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>32371.93</v>
+        <v>29937.69</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1759303006389532</v>
+        <v>0.2378970547055978</v>
       </c>
     </row>
     <row r="15">
@@ -3646,13 +3646,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>15918.25</v>
+        <v>18352.49</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34646.193</v>
+        <v>32211.953</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3148111411016631</v>
+        <v>0.3629524802636508</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1148.4</v>
+        <v>3521.1</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>68.23</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>3 de 30</t>
+          <t>4 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1148.4</v>
+        <v>3521.1</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>4000</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>68.23</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>11295.33</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>18024.72</v>
+        <v>20465.65</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3264,7 +3264,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3435,13 +3435,13 @@
         <v>655</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1148.4</v>
+        <v>3521.1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-493.4000000000001</v>
+        <v>-2866.1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.753282442748092</v>
+        <v>5.375725190839694</v>
       </c>
     </row>
     <row r="8">
@@ -3603,13 +3603,13 @@
         <v>39283</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9345.309999999999</v>
+        <v>9413.540000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29937.69</v>
+        <v>29869.46</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2378970547055978</v>
+        <v>0.2396339383448311</v>
       </c>
     </row>
     <row r="15">
@@ -3646,13 +3646,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18352.49</v>
+        <v>20793.42</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32211.953</v>
+        <v>29771.023</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3629524802636508</v>
+        <v>0.4112261258370828</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>935.78</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>16784.12</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2366,52 +2366,52 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
+          <t>2 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
           <t>1 de 30</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>0 de 30</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>1 de 30</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>1 de 30</t>
-        </is>
-      </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>4 de 30</t>
+          <t>5 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3061,7 +3061,7 @@
         <v>-633.71</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>17719.9</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>11295.33</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>20465.65</v>
+        <v>38185.55</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3263,7 +3263,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3339,13 +3339,13 @@
         <v>3800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7495.2</v>
+        <v>8430.98</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3695.2</v>
+        <v>-4630.98</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.972421052631579</v>
+        <v>2.218678947368421</v>
       </c>
     </row>
     <row r="4">
@@ -3603,13 +3603,13 @@
         <v>39283</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9413.540000000001</v>
+        <v>26197.66</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29869.46</v>
+        <v>13085.34</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2396339383448311</v>
+        <v>0.6668956036962553</v>
       </c>
     </row>
     <row r="15">
@@ -3646,13 +3646,13 @@
         <v>50564.443</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>20793.42</v>
+        <v>38513.32</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>29771.023</v>
+        <v>12051.123</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4112261258370828</v>
+        <v>0.7616680361731661</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>216.47</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>327.77</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3521.1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2146.66</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>935.78</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>16784.12</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>68.23</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7495.2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6982.18</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>1 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>5 de 30</t>
+          <t>0 de 30</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2456,10 +2456,10 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2476,22 +2476,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>5291.95</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5291.95</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -2569,10 +2569,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>67.44</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67.44</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>71.11</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>71.11</v>
+        <v>216.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>216.47</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>500</v>
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2297.69</v>
+        <v>1462.41</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1462.41</v>
+        <v>3302.63</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3302.63</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>3850.98</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3850.98</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3425.52</v>
+        <v>-16.52</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-16.52</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>3521.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3521.1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>4000</v>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>189.57</v>
+        <v>1830.03</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1830.03</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -2893,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>3336.4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3336.4</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -2944,16 +2944,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>1882.63</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1882.63</v>
+        <v>54.72</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>54.72</v>
+        <v>35.81</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>35.81</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>1500</v>
@@ -2974,13 +2974,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>4927.44</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4927.44</v>
+        <v>2146.66</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2146.66</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -3052,16 +3052,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>19574.65</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>19574.65</v>
+        <v>-633.71</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-633.71</v>
+        <v>17719.9</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>17719.9</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>515.26</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>68.23</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>68.23</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1000</v>
@@ -3160,13 +3160,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>583</v>
+        <v>738.77</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>738.77</v>
+        <v>169.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>169.3</v>
+        <v>4602.41</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>9544.01</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>14477.38</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>14477.38</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>10000</v>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="29">
       <c r="C29" s="6" t="n">
-        <v>16577.79</v>
+        <v>34614.9</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>34614.9</v>
+        <v>11295.33</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>11295.33</v>
+        <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>38185.55</v>
+        <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1113,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>3780.48</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0 de 30</t>
+          <t>1 de 30</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>3780.48</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>3780.48</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -3263,9 +3263,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3336,16 +3336,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8430.98</v>
+        <v>3780.48</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-4630.98</v>
+        <v>-980.48</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.218678947368421</v>
+        <v>1.350171428571429</v>
       </c>
     </row>
     <row r="4">
@@ -3363,13 +3363,13 @@
         <v>3973</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>35.81</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3937.19</v>
+        <v>3973</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.009013340045305815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3432,16 +3432,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>655</v>
+        <v>210</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3521.1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-2866.1</v>
+        <v>210</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5.375725190839694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3456,13 +3456,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>463</v>
+        <v>105</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>463</v>
+        <v>105</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -3579,13 +3579,13 @@
         <v>960</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>327.77</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>632.23</v>
+        <v>960</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3414270833333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3600,16 +3600,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>39283</v>
+        <v>37403.61</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26197.66</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13085.34</v>
+        <v>37403.61</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6668956036962553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3643,16 +3643,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>50564.443</v>
+        <v>46882.053</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>38513.32</v>
+        <v>3780.48</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12051.123</v>
+        <v>43101.573</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.7616680361731661</v>
+        <v>0.08063810686788823</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NIZA ARIAS YOSELIN EDITH</t>
+          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TAMAYO VILLACIS EDWIN XAVIER</t>
+          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOSCANO RAMIREZ MONICA CECILIA</t>
+          <t>VARIEDADES-PAS SAS</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VARIEDADES-PAS SAS</t>
+          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VELASQUEZ ARELLANO SAIRA MAGDALENA</t>
+          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VIDAL VARGAS ANDREA DOMINIQUE</t>
+          <t>ZAMBRANO ANGELA MARIA</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2299,144 +2299,84 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RIOS CARRION ANGEL BENIGNO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ZAMBRANO ANGELA MARIA</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>1 de 30</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
         </is>
       </c>
     </row>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
+        <v>-95.7</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
@@ -2785,7 +2785,7 @@
         <v>3521.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>-95.7</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>4000</v>
@@ -3180,7 +3180,7 @@
         <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3780.48</v>
+        <v>3684.78</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3205,7 +3205,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3375,13 +3375,13 @@
         <v>210</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>-95.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>210</v>
+        <v>305.7</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>-0.4557142857142857</v>
       </c>
     </row>
     <row r="8">
@@ -3586,13 +3586,13 @@
         <v>46882.053</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3780.48</v>
+        <v>3684.78</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>43101.573</v>
+        <v>43197.273</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.08063810686788823</v>
+        <v>0.07859681400897696</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
         <v>17719.9</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3684.78</v>
+        <v>3702.69</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3471,13 +3471,13 @@
         <v>203.763</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>203.763</v>
+        <v>185.853</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.0878962323876268</v>
       </c>
     </row>
     <row r="12">
@@ -3586,13 +3586,13 @@
         <v>46882.053</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3684.78</v>
+        <v>3702.69</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>43197.273</v>
+        <v>43179.363</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.07859681400897696</v>
+        <v>0.0789788365283406</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>-68.23</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>68.23</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>-68.23</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>1000</v>
@@ -3180,7 +3180,7 @@
         <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3702.69</v>
+        <v>3634.46</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3205,7 +3205,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3543,13 +3543,13 @@
         <v>37403.61</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>-68.23</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37403.61</v>
+        <v>37471.84</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>-0.001824155475901925</v>
       </c>
     </row>
     <row r="15">
@@ -3586,13 +3586,13 @@
         <v>46882.053</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3702.69</v>
+        <v>3634.46</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>43179.363</v>
+        <v>43247.59299999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.0789788365283406</v>
+        <v>0.07752348217344492</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>233.66</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>14878.95</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2569,7 +2569,7 @@
         <v>216.47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>233.66</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>500</v>
@@ -3001,7 +3001,7 @@
         <v>17719.9</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>17.91</v>
+        <v>14896.86</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3634.46</v>
+        <v>18747.07</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3203,9 +3203,9 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3543,13 +3543,13 @@
         <v>37403.61</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-68.23</v>
+        <v>15044.38</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37471.84</v>
+        <v>22359.23</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-0.001824155475901925</v>
+        <v>0.4022173260816269</v>
       </c>
     </row>
     <row r="15">
@@ -3586,13 +3586,13 @@
         <v>46882.053</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3634.46</v>
+        <v>18747.07</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>43247.59299999999</v>
+        <v>28134.983</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.07752348217344492</v>
+        <v>0.3998773261913253</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIOS CARRION ANGEL BENIGNO.xlsx
+++ b/data/RIOS CARRION ANGEL BENIGNO.xlsx
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3109,7 +3109,7 @@
         <v>4602.41</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>3000</v>
@@ -3180,7 +3180,7 @@
         <v>42787.96</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>18747.07</v>
+        <v>18764.98</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>38500</v>
@@ -3471,13 +3471,13 @@
         <v>203.763</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17.91</v>
+        <v>35.82</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>185.853</v>
+        <v>167.943</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.0878962323876268</v>
+        <v>0.1757924647752536</v>
       </c>
     </row>
     <row r="12">
@@ -3586,13 +3586,13 @@
         <v>46882.053</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>18747.07</v>
+        <v>18764.98</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28134.983</v>
+        <v>28117.073</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3998773261913253</v>
+        <v>0.4002593487106889</v>
       </c>
     </row>
   </sheetData>
